--- a/data/sxbet/ligas/Primera Division/trades.xlsx
+++ b/data/sxbet/ligas/Primera Division/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
+          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785193080</t>
+          <t>1785196536</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>90.961538</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
+          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,23 +651,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -682,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785192947</t>
+          <t>1785195634</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>102.88172</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +755,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
+          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785192847</t>
+          <t>1785193080</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
+          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -890,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -920,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785192834</t>
+          <t>1785192947</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
+          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1024,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785192821</t>
+          <t>1785192847</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1051,23 +1067,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
+          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1128,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785192691</t>
+          <t>1785192834</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1138,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>9.367681</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
+          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1166,12 +1182,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19.35809</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1232,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785192659</t>
+          <t>1785192821</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1242,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36.268084</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,23 +1275,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
+          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25.4851</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1336,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785192641</t>
+          <t>1785192691</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1346,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>48.085094</t>
+          <t>9.367681</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1363,28 +1379,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
+          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19.35809</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1410,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1440,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785192634</t>
+          <t>1785192659</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1450,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>58.874459</t>
+          <t>36.268084</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1467,7 +1483,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
+          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1478,12 +1494,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25.71451</t>
+          <t>25.4851</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1544,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785192633</t>
+          <t>1785192641</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1554,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48.064505</t>
+          <t>48.085094</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1571,28 +1587,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
+          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1618,7 +1634,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1648,7 +1664,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785192460</t>
+          <t>1785192634</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1658,7 +1674,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>58.874459</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1675,23 +1691,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
+          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.71451</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1752,7 +1768,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785192458</t>
+          <t>1785192633</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1762,7 +1778,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>48.064505</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1779,23 +1795,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
+          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25.41551</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1856,7 +1872,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785192439</t>
+          <t>1785192460</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1866,7 +1882,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>48.295506</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1883,23 +1899,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
+          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1960,7 +1976,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785192425</t>
+          <t>1785192458</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1970,7 +1986,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1987,7 +2003,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
+          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1998,12 +2014,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>25.41551</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2064,7 +2080,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785192400</t>
+          <t>1785192439</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2074,7 +2090,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>48.295506</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2091,7 +2107,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
+          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2102,7 +2118,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25.35348</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2168,7 +2184,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785192383</t>
+          <t>1785192425</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2178,7 +2194,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>48.063469</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2195,7 +2211,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
+          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2206,12 +2222,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25.3385</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2272,7 +2288,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785192344</t>
+          <t>1785192400</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2282,7 +2298,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>47.808491</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2299,27 +2315,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
+          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>25.35348</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2327,26 +2339,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -2384,7 +2392,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785192020</t>
+          <t>1785192383</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2394,7 +2402,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>60.183673</t>
+          <t>48.063469</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2411,27 +2419,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
+          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>83.37098</t>
+          <t>25.3385</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2439,26 +2443,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785191983</t>
+          <t>1785192344</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>167.15986</t>
+          <t>47.808491</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2523,7 +2523,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
+          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2538,12 +2538,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21.25099</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785191956</t>
+          <t>1785192020</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>42.608501</t>
+          <t>60.183673</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
+          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>83.37098</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785191607</t>
+          <t>1785191983</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>132.591479</t>
+          <t>167.15986</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,31 +2747,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
+          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>21.25099</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2794,7 +2802,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2824,7 +2832,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785190879</t>
+          <t>1785191956</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2834,7 +2842,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>46.308571</t>
+          <t>42.608501</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,12 +2859,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
+          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2866,39 +2874,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3525</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -2906,7 +2914,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2936,7 +2944,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785191607</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2946,7 +2954,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>139.687943</t>
+          <t>132.591479</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,54 +2971,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785190879</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>46.308571</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3075,7 +3075,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3525</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>139.687943</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3187,23 +3187,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3211,7 +3215,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3234,7 +3242,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3264,7 +3272,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3274,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>20.671835</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3291,31 +3299,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>192.07656</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3338,7 +3354,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3368,7 +3384,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3378,7 +3394,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>301.296565</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3395,7 +3411,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3406,12 +3422,12 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3442,7 +3458,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3472,7 +3488,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3482,7 +3498,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>323.324675</t>
+          <t>20.671835</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3499,7 +3515,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3510,17 +3526,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>192.07656</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3546,7 +3562,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3576,7 +3592,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3586,7 +3602,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>301.296565</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3603,39 +3619,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.99021</t>
+          <t>155.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3658,7 +3666,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3688,7 +3696,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785189854</t>
+          <t>1785190745</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3698,7 +3706,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>24.643012</t>
+          <t>323.324675</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3715,27 +3723,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3743,11 +3747,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785189648</t>
+          <t>1785190745</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>24.691358</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3827,110 +3827,334 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4.99021</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785189854</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>24.643012</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785189648</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>24.691358</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>0x75149a4dcb7aa5d35fc6692d21303104765eb2330e7b582a2136cd6202de3543</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>2.83937</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>1.2025</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Union La Calera -1</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>Union La Calera vs Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>L19474445</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>1785189616</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>1785193200</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>14.02158</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Division/trades.xlsx
+++ b/data/sxbet/ligas/Primera Division/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
+          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785196536</t>
+          <t>1785269304</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>90.961538</t>
+          <t>14.601681</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
+          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3487</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785195634</t>
+          <t>1785196536</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>102.88172</t>
+          <t>90.961538</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
+          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -763,23 +763,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785193080</t>
+          <t>1785195634</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>102.88172</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
+          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -936,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785192947</t>
+          <t>1785193080</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -963,28 +971,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
+          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1010,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785192847</t>
+          <t>1785192947</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
+          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1144,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785192834</t>
+          <t>1785192847</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1171,7 +1179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
+          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785192821</t>
+          <t>1785192834</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1275,23 +1283,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
+          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1352,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785192691</t>
+          <t>1785192821</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>9.367681</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,18 +1387,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
+          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19.35809</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1456,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785192659</t>
+          <t>1785192691</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1474,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36.268084</t>
+          <t>9.367681</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,7 +1491,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
+          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1494,12 +1502,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25.4851</t>
+          <t>19.35809</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1560,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785192641</t>
+          <t>1785192659</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48.085094</t>
+          <t>36.268084</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,28 +1595,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
+          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25.4851</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1634,7 +1642,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1664,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785192634</t>
+          <t>1785192641</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1674,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>58.874459</t>
+          <t>48.085094</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,28 +1699,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
+          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25.71451</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1738,7 +1746,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1768,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785192633</t>
+          <t>1785192634</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.064505</t>
+          <t>58.874459</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,23 +1803,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
+          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.71451</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1872,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785192460</t>
+          <t>1785192633</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1882,7 +1890,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>48.064505</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,7 +1907,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
+          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1976,7 +1984,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785192458</t>
+          <t>1785192460</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2003,23 +2011,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
+          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25.41551</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2080,7 +2088,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785192439</t>
+          <t>1785192458</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2090,7 +2098,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.295506</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,7 +2115,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
+          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2118,12 +2126,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>25.41551</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2184,7 +2192,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785192425</t>
+          <t>1785192439</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2194,7 +2202,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>48.295506</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,7 +2219,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
+          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2288,7 +2296,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785192400</t>
+          <t>1785192425</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2315,7 +2323,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
+          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2326,7 +2334,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25.35348</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2392,7 +2400,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785192383</t>
+          <t>1785192400</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2402,7 +2410,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>48.063469</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2419,7 +2427,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
+          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2430,12 +2438,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.3385</t>
+          <t>25.35348</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2496,7 +2504,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785192344</t>
+          <t>1785192383</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2506,7 +2514,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>47.808491</t>
+          <t>48.063469</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2523,27 +2531,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
+          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>25.3385</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2551,26 +2555,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785192020</t>
+          <t>1785192344</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>60.183673</t>
+          <t>47.808491</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
+          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>83.37098</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785191983</t>
+          <t>1785192020</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>167.15986</t>
+          <t>60.183673</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
+          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21.25099</t>
+          <t>83.37098</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785191956</t>
+          <t>1785191983</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>42.608501</t>
+          <t>167.15986</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,7 +2859,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
+          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>21.25099</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785191607</t>
+          <t>1785191956</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>132.591479</t>
+          <t>42.608501</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2971,31 +2971,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
+          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3018,7 +3026,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3048,7 +3056,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785190879</t>
+          <t>1785191607</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3058,7 +3066,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>46.308571</t>
+          <t>132.591479</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3075,27 +3083,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
+          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3525</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3103,26 +3107,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785190879</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>139.687943</t>
+          <t>46.308571</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3187,7 +3187,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3202,17 +3202,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3525</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>139.687943</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,7 +3299,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3411,23 +3411,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3435,7 +3439,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3488,7 +3496,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3498,7 +3506,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>20.671835</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3515,7 +3523,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3526,17 +3534,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>192.07656</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3562,7 +3570,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3602,7 +3610,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>301.296565</t>
+          <t>20.671835</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3619,7 +3627,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3630,17 +3638,17 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>192.07656</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3666,7 +3674,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3696,7 +3704,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3706,7 +3714,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>323.324675</t>
+          <t>301.296565</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3723,7 +3731,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3734,17 +3742,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>155.6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3770,7 +3778,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3810,7 +3818,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>323.324675</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3827,27 +3835,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.99021</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3855,11 +3859,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785189854</t>
+          <t>1785190745</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>24.643012</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3939,12 +3939,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99021</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785189648</t>
+          <t>1785189854</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>24.691358</t>
+          <t>24.643012</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4051,110 +4051,222 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785189648</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>24.691358</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>0x75149a4dcb7aa5d35fc6692d21303104765eb2330e7b582a2136cd6202de3543</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>2.83937</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>1.2025</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Union La Calera -1</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>Union La Calera vs Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>L19474445</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>1785189616</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>1785193200</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>14.02158</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Division/trades.xlsx
+++ b/data/sxbet/ligas/Primera Division/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
+          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785269304</t>
+          <t>1785345042</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>14.601681</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
+          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785196536</t>
+          <t>1785269304</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>90.961538</t>
+          <t>14.601681</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
+          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3487</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785195634</t>
+          <t>1785196536</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>102.88172</t>
+          <t>90.961538</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
+          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -875,23 +875,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -914,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785193080</t>
+          <t>1785195634</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>102.88172</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
+          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1048,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785192947</t>
+          <t>1785193080</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1075,28 +1083,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
+          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1122,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785192847</t>
+          <t>1785192947</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
+          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1256,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785192834</t>
+          <t>1785192847</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1283,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
+          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1360,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785192821</t>
+          <t>1785192834</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1387,23 +1395,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
+          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1464,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785192691</t>
+          <t>1785192821</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>9.367681</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,18 +1499,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
+          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.35809</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1568,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785192659</t>
+          <t>1785192691</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1586,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36.268084</t>
+          <t>9.367681</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,7 +1603,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
+          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1606,12 +1614,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25.4851</t>
+          <t>19.35809</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1672,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785192641</t>
+          <t>1785192659</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1682,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.085094</t>
+          <t>36.268084</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,28 +1707,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
+          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25.4851</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1746,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1776,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785192634</t>
+          <t>1785192641</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1786,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>58.874459</t>
+          <t>48.085094</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,28 +1811,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
+          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25.71451</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1850,7 +1858,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1880,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785192633</t>
+          <t>1785192634</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1890,7 +1898,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>48.064505</t>
+          <t>58.874459</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,23 +1915,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
+          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.71451</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1984,7 +1992,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785192460</t>
+          <t>1785192633</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1994,7 +2002,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>48.064505</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,7 +2019,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
+          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2088,7 +2096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785192458</t>
+          <t>1785192460</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2115,23 +2123,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
+          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25.41551</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2192,7 +2200,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785192439</t>
+          <t>1785192458</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2202,7 +2210,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>48.295506</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,7 +2227,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
+          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2230,12 +2238,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>25.41551</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2296,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785192425</t>
+          <t>1785192439</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2306,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>48.295506</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,7 +2331,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
+          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2400,7 +2408,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785192400</t>
+          <t>1785192425</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2427,7 +2435,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
+          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2438,7 +2446,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.35348</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2504,7 +2512,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785192383</t>
+          <t>1785192400</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2514,7 +2522,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.063469</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2531,7 +2539,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
+          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2542,12 +2550,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.3385</t>
+          <t>25.35348</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2608,7 +2616,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785192344</t>
+          <t>1785192383</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2618,7 +2626,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>47.808491</t>
+          <t>48.063469</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2635,27 +2643,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
+          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>25.3385</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2663,26 +2667,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785192020</t>
+          <t>1785192344</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>60.183673</t>
+          <t>47.808491</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
+          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>83.37098</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785191983</t>
+          <t>1785192020</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>167.15986</t>
+          <t>60.183673</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,7 +2859,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
+          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21.25099</t>
+          <t>83.37098</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785191956</t>
+          <t>1785191983</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>42.608501</t>
+          <t>167.15986</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
+          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>21.25099</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785191607</t>
+          <t>1785191956</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>132.591479</t>
+          <t>42.608501</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3083,31 +3083,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
+          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3130,7 +3138,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3160,7 +3168,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785190879</t>
+          <t>1785191607</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3170,7 +3178,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>46.308571</t>
+          <t>132.591479</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3187,27 +3195,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
+          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3525</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3215,26 +3219,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785190879</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>139.687943</t>
+          <t>46.308571</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,7 +3299,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3525</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>139.687943</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3411,7 +3411,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3523,23 +3523,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3547,7 +3551,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3600,7 +3608,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3610,7 +3618,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20.671835</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,7 +3635,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3638,17 +3646,17 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>192.07656</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3674,7 +3682,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3714,7 +3722,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>301.296565</t>
+          <t>20.671835</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,7 +3739,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3742,17 +3750,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>192.07656</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3778,7 +3786,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3808,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3818,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>323.324675</t>
+          <t>301.296565</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3835,7 +3843,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3846,17 +3854,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>155.6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3882,7 +3890,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3922,7 +3930,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>323.324675</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3939,27 +3947,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4.99021</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3967,11 +3971,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785189854</t>
+          <t>1785190745</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>24.643012</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4051,12 +4051,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99021</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785189648</t>
+          <t>1785189854</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>24.691358</t>
+          <t>24.643012</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4163,110 +4163,222 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785189648</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>24.691358</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>0x75149a4dcb7aa5d35fc6692d21303104765eb2330e7b582a2136cd6202de3543</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>2.83937</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>1.2025</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Union La Calera -1</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>Union La Calera vs Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>L19474445</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>1785189616</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>1785193200</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>14.02158</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Division/trades.xlsx
+++ b/data/sxbet/ligas/Primera Division/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
+          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19615611</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785345042</t>
+          <t>1785441528</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>180.756098</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
+          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>75.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19615611</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785269304</t>
+          <t>1785441518</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>14.601681</t>
+          <t>186.773994</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
+          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785196536</t>
+          <t>1785345042</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>90.961538</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
+          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3487</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
+          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785195634</t>
+          <t>1785269304</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>102.88172</t>
+          <t>14.601681</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,23 +979,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
+          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1003,7 +1007,11 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1056,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785193080</t>
+          <t>1785196536</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>90.961538</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1091,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
+          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1091,23 +1099,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1130,7 +1146,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1176,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785192947</t>
+          <t>1785195634</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1186,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>102.88172</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,28 +1203,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
+          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1234,7 +1250,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785192847</t>
+          <t>1785193080</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,28 +1307,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
+          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1338,7 +1354,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785192834</t>
+          <t>1785192947</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
+          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1472,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785192821</t>
+          <t>1785192847</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1499,23 +1515,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
+          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1576,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785192691</t>
+          <t>1785192834</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1586,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>9.367681</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,7 +1619,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
+          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1614,12 +1630,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19.35809</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1680,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785192659</t>
+          <t>1785192821</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>36.268084</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,23 +1723,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
+          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25.4851</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1784,7 +1800,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785192641</t>
+          <t>1785192691</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1794,7 +1810,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.085094</t>
+          <t>9.367681</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,28 +1827,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
+          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19.35809</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1858,7 +1874,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1888,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785192634</t>
+          <t>1785192659</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1914,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>58.874459</t>
+          <t>36.268084</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,7 +1931,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
+          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1926,12 +1942,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25.71451</t>
+          <t>25.4851</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1992,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785192633</t>
+          <t>1785192641</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2002,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.064505</t>
+          <t>48.085094</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,28 +2035,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
+          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2066,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2096,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785192460</t>
+          <t>1785192634</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2106,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>58.874459</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,23 +2139,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
+          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.71451</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2200,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785192458</t>
+          <t>1785192633</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2210,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>48.064505</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,23 +2243,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
+          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25.41551</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2304,7 +2320,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785192439</t>
+          <t>1785192460</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2314,7 +2330,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>48.295506</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,23 +2347,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
+          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2408,7 +2424,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785192425</t>
+          <t>1785192458</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2434,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,7 +2451,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
+          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2446,12 +2462,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>25.41551</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2512,7 +2528,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785192400</t>
+          <t>1785192439</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2522,7 +2538,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>48.295506</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,7 +2555,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
+          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2550,7 +2566,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.35348</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2616,7 +2632,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785192383</t>
+          <t>1785192425</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2642,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.063469</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,7 +2659,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
+          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2654,12 +2670,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25.3385</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2720,7 +2736,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785192344</t>
+          <t>1785192400</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2746,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>47.808491</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,27 +2763,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
+          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>25.35348</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2775,26 +2787,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -2832,7 +2840,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785192020</t>
+          <t>1785192383</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2842,7 +2850,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>60.183673</t>
+          <t>48.063469</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,27 +2867,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
+          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>83.37098</t>
+          <t>25.3385</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2887,26 +2891,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785191983</t>
+          <t>1785192344</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>167.15986</t>
+          <t>47.808491</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
+          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21.25099</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785191956</t>
+          <t>1785192020</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>42.608501</t>
+          <t>60.183673</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
+          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>83.37098</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785191607</t>
+          <t>1785191983</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>132.591479</t>
+          <t>167.15986</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,31 +3195,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
+          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>21.25099</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3242,7 +3250,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3272,7 +3280,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785190879</t>
+          <t>1785191956</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3282,7 +3290,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>46.308571</t>
+          <t>42.608501</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,12 +3307,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
+          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3314,39 +3322,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3525</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3354,7 +3362,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3384,7 +3392,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785191607</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3394,7 +3402,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>139.687943</t>
+          <t>132.591479</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3411,54 +3419,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785190879</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>46.308571</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3538,22 +3538,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3525</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>139.687943</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3635,23 +3635,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3659,7 +3663,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3682,7 +3690,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3712,7 +3720,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3722,7 +3730,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>20.671835</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3739,31 +3747,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>192.07656</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3786,7 +3802,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3816,7 +3832,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3826,7 +3842,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>301.296565</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,7 +3859,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3854,12 +3870,12 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3890,7 +3906,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3920,7 +3936,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3930,7 +3946,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>323.324675</t>
+          <t>20.671835</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3947,7 +3963,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3958,17 +3974,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>192.07656</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3994,7 +4010,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4024,7 +4040,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4034,7 +4050,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>301.296565</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4051,39 +4067,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.99021</t>
+          <t>155.6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4106,7 +4114,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4136,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785189854</t>
+          <t>1785190745</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4146,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>24.643012</t>
+          <t>323.324675</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4163,27 +4171,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4191,11 +4195,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785189648</t>
+          <t>1785190745</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>24.691358</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4275,110 +4275,334 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4.99021</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785189854</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>24.643012</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785189648</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>24.691358</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>0x75149a4dcb7aa5d35fc6692d21303104765eb2330e7b582a2136cd6202de3543</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>2.83937</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>1.2025</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Union La Calera -1</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>Union La Calera vs Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>L19474445</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>1785189616</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>1785193200</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>14.02158</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Division/trades.xlsx
+++ b/data/sxbet/ligas/Primera Division/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
+          <t>0x44e0e19da66aa09249da7de981a92039f9257de3fd68452ab2d431e7e40fb952</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785441528</t>
+          <t>1785459482</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>180.756098</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
+          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>75.41</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4038</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785441518</t>
+          <t>1785441528</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>186.773994</t>
+          <t>180.756098</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
+          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75.41</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19615611</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785345042</t>
+          <t>1785441518</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>186.773994</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
+          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785269304</t>
+          <t>1785345042</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>14.601681</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,12 +979,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
+          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -994,22 +994,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785196536</t>
+          <t>1785269304</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>90.961538</t>
+          <t>14.601681</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,12 +1091,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
+          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1106,22 +1106,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3487</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785195634</t>
+          <t>1785196536</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>102.88172</t>
+          <t>90.961538</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
+          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1211,23 +1211,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1250,7 +1258,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1280,7 +1288,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785193080</t>
+          <t>1785195634</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1298,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>102.88172</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1315,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
+          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1384,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785192947</t>
+          <t>1785193080</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1411,28 +1419,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
+          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1458,7 +1466,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785192847</t>
+          <t>1785192947</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
+          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1592,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785192834</t>
+          <t>1785192847</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1619,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
+          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785192821</t>
+          <t>1785192834</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1723,23 +1731,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
+          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1800,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785192691</t>
+          <t>1785192821</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1810,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>9.367681</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,18 +1835,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
+          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.35809</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1904,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785192659</t>
+          <t>1785192691</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1914,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36.268084</t>
+          <t>9.367681</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
+          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1942,12 +1950,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25.4851</t>
+          <t>19.35809</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2008,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785192641</t>
+          <t>1785192659</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.085094</t>
+          <t>36.268084</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,28 +2043,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
+          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25.4851</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2082,7 +2090,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785192634</t>
+          <t>1785192641</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>58.874459</t>
+          <t>48.085094</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,28 +2147,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
+          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25.71451</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2186,7 +2194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2216,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785192633</t>
+          <t>1785192634</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>48.064505</t>
+          <t>58.874459</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,23 +2251,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
+          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.71451</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2320,7 +2328,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785192460</t>
+          <t>1785192633</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2330,7 +2338,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>48.064505</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,7 +2355,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
+          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2424,7 +2432,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785192458</t>
+          <t>1785192460</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2451,23 +2459,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
+          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.41551</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2528,7 +2536,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785192439</t>
+          <t>1785192458</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2538,7 +2546,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.295506</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,7 +2563,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
+          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2566,12 +2574,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>25.41551</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2632,7 +2640,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785192425</t>
+          <t>1785192439</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2642,7 +2650,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>48.295506</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2659,7 +2667,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
+          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2736,7 +2744,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785192400</t>
+          <t>1785192425</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2763,7 +2771,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
+          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2774,7 +2782,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25.35348</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2840,7 +2848,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785192383</t>
+          <t>1785192400</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2850,7 +2858,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>48.063469</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2867,7 +2875,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
+          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2878,12 +2886,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25.3385</t>
+          <t>25.35348</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2944,7 +2952,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785192344</t>
+          <t>1785192383</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2954,7 +2962,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>47.808491</t>
+          <t>48.063469</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2971,27 +2979,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
+          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>25.3385</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2999,26 +3003,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785192020</t>
+          <t>1785192344</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>60.183673</t>
+          <t>47.808491</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
+          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>83.37098</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785191983</t>
+          <t>1785192020</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>167.15986</t>
+          <t>60.183673</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
+          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21.25099</t>
+          <t>83.37098</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785191956</t>
+          <t>1785191983</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>42.608501</t>
+          <t>167.15986</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
+          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>21.25099</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785191607</t>
+          <t>1785191956</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>132.591479</t>
+          <t>42.608501</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,31 +3419,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
+          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3466,7 +3474,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3496,7 +3504,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785190879</t>
+          <t>1785191607</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3506,7 +3514,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>46.308571</t>
+          <t>132.591479</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,27 +3531,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
+          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3525</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3551,26 +3555,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785190879</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>139.687943</t>
+          <t>46.308571</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3635,7 +3635,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3650,17 +3650,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3525</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>139.687943</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3859,23 +3859,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3883,7 +3887,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3936,7 +3944,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3946,7 +3954,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>20.671835</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3963,7 +3971,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3974,17 +3982,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>192.07656</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4010,7 +4018,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4050,7 +4058,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>301.296565</t>
+          <t>20.671835</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4067,7 +4075,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4078,17 +4086,17 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>192.07656</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4114,7 +4122,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4144,7 +4152,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4154,7 +4162,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>323.324675</t>
+          <t>301.296565</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,7 +4179,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4182,17 +4190,17 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>155.6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4218,7 +4226,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4258,7 +4266,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>323.324675</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4275,27 +4283,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.99021</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4303,11 +4307,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785189854</t>
+          <t>1785190745</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>24.643012</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,12 +4387,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99021</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785189648</t>
+          <t>1785189854</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>24.691358</t>
+          <t>24.643012</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4499,110 +4499,222 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785189648</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>24.691358</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>0x75149a4dcb7aa5d35fc6692d21303104765eb2330e7b582a2136cd6202de3543</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>2.83937</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>1.2025</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Union La Calera -1</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>Union La Calera vs Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>L19474445</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>1785189616</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>1785193200</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>14.02158</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Division/trades.xlsx
+++ b/data/sxbet/ligas/Primera Division/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x44e0e19da66aa09249da7de981a92039f9257de3fd68452ab2d431e7e40fb952</t>
+          <t>0xa6662351ed0cdd3219611c5844d3f542df082c943aa81df2efe3eb02cf0c52aa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>12.85893</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,26 +555,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Cobresal vs Union La Calera</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Cobresal vs Union La Calera</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Union La Calera</t>
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785459482</t>
+          <t>1785461587</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>21.88754</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,27 +635,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
+          <t>0xb963fb285adc1787ddf4ca4632c560dc9fdd9575b3cbfb29621fa14f9fd1f787</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>12.85225</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -671,26 +659,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Cobresal vs Union La Calera</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Cobresal vs Union La Calera</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Union La Calera</t>
@@ -728,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785441528</t>
+          <t>1785460982</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>180.756098</t>
+          <t>21.87617</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,27 +739,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
+          <t>0x359dd1d25732d3b83d3e7b63e7453929f93cc1f4450a4464e839d81eb8e93766</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>75.41</t>
+          <t>12.94614</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4038</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -783,26 +763,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cobresal vs Union La Calera</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Cobresal vs Union La Calera</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Union La Calera</t>
@@ -840,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785441518</t>
+          <t>1785460380</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>186.773994</t>
+          <t>22.035983</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +843,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
+          <t>0x44e0e19da66aa09249da7de981a92039f9257de3fd68452ab2d431e7e40fb952</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,12 +858,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -897,7 +873,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -907,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19615611</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785345042</t>
+          <t>1785459482</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,12 +955,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
+          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -994,22 +970,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19615611</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785269304</t>
+          <t>1785441528</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>14.601681</t>
+          <t>180.756098</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,12 +1067,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
+          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1106,22 +1082,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>75.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1131,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1176,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785196536</t>
+          <t>1785441518</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>90.961538</t>
+          <t>186.773994</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
+          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1218,12 +1194,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3487</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1233,7 +1209,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1243,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1288,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785195634</t>
+          <t>1785345042</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>102.88172</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1315,31 +1291,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
+          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1347,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785193080</t>
+          <t>1785269304</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>14.601681</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,23 +1403,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
+          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1443,7 +1431,11 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1496,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785192947</t>
+          <t>1785196536</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1506,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>90.961538</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,31 +1515,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
+          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785192847</t>
+          <t>1785195634</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>102.88172</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,28 +1627,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
+          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785192834</t>
+          <t>1785193080</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,28 +1731,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
+          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785192821</t>
+          <t>1785192947</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,23 +1835,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
+          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785192691</t>
+          <t>1785192847</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>9.367681</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
+          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1950,12 +1950,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19.35809</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785192659</t>
+          <t>1785192834</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>36.268084</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,7 +2043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
+          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2054,12 +2054,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25.4851</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785192641</t>
+          <t>1785192821</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.085094</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,28 +2147,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
+          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785192634</t>
+          <t>1785192691</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>58.874459</t>
+          <t>9.367681</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
+          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2262,12 +2262,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25.71451</t>
+          <t>19.35809</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785192633</t>
+          <t>1785192659</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>48.064505</t>
+          <t>36.268084</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,23 +2355,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
+          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.4851</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785192460</t>
+          <t>1785192641</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>48.085094</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,28 +2459,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
+          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785192458</t>
+          <t>1785192634</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>58.874459</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,7 +2563,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
+          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2574,12 +2574,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.41551</t>
+          <t>25.71451</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785192439</t>
+          <t>1785192633</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.295506</t>
+          <t>48.064505</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,23 +2667,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
+          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785192425</t>
+          <t>1785192460</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,23 +2771,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
+          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785192400</t>
+          <t>1785192458</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
+          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2886,12 +2886,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25.35348</t>
+          <t>25.41551</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785192383</t>
+          <t>1785192439</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.063469</t>
+          <t>48.295506</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
+          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2990,12 +2990,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25.3385</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785192344</t>
+          <t>1785192425</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>47.808491</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3083,27 +3083,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
+          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3111,26 +3107,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3168,7 +3160,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785192020</t>
+          <t>1785192400</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3178,7 +3170,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>60.183673</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,27 +3187,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
+          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>83.37098</t>
+          <t>25.35348</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3223,26 +3211,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3280,7 +3264,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785191983</t>
+          <t>1785192383</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3290,7 +3274,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>167.15986</t>
+          <t>48.063469</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3307,27 +3291,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
+          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21.25099</t>
+          <t>25.3385</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3335,26 +3315,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3392,7 +3368,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785191956</t>
+          <t>1785192344</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3402,7 +3378,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>42.608501</t>
+          <t>47.808491</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,7 +3395,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
+          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,12 +3410,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3449,7 +3425,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3474,7 +3450,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3504,7 +3480,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785191607</t>
+          <t>1785192020</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3514,7 +3490,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>132.591479</t>
+          <t>60.183673</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3531,31 +3507,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
+          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>83.37098</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3578,7 +3562,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3608,7 +3592,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785190879</t>
+          <t>1785191983</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3618,7 +3602,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>46.308571</t>
+          <t>167.15986</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3635,12 +3619,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
+          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3650,17 +3634,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>21.25099</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3525</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3690,7 +3674,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3720,7 +3704,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785191956</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3730,7 +3714,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>139.687943</t>
+          <t>42.608501</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3747,12 +3731,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3762,12 +3746,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3777,24 +3761,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3802,7 +3786,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3832,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785191607</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3842,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>132.591479</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3859,39 +3843,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Union La Calera 0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3914,7 +3890,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3944,7 +3920,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785190879</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3954,7 +3930,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>46.308571</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3971,31 +3947,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.3525</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4018,7 +4002,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4048,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4058,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>20.671835</t>
+          <t>139.687943</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4075,31 +4059,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>192.07656</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4122,7 +4114,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4152,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4162,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>301.296565</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4179,23 +4171,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4203,7 +4199,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>323.324675</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,17 +4294,17 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>20.671835</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,39 +4387,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.99021</t>
+          <t>192.07656</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4442,7 +4434,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4472,7 +4464,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785189854</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4482,7 +4474,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>24.643012</t>
+          <t>301.296565</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4499,39 +4491,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>155.6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4554,7 +4538,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4584,7 +4568,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785189648</t>
+          <t>1785190745</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4594,7 +4578,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>24.691358</t>
+          <t>323.324675</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4611,110 +4595,438 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.8125</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785190745</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4.99021</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785189854</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>24.643012</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785189648</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>24.691358</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>0x75149a4dcb7aa5d35fc6692d21303104765eb2330e7b582a2136cd6202de3543</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>2.83937</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>1.2025</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Union La Calera -1</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>Union La Calera vs Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>L19474445</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>1785189616</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>1785193200</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>14.02158</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Division/trades.xlsx
+++ b/data/sxbet/ligas/Primera Division/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xa6662351ed0cdd3219611c5844d3f542df082c943aa81df2efe3eb02cf0c52aa</t>
+          <t>0xabdf4fe38efdf58bf8d47e567216699ec84fc0c25cc103f8e4cde0a12f422be5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.85893</t>
+          <t>56.61</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xde65f43d12cd96e371220e4b3864b8dfadf5a71d384749b19b33947eed003295</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785461587</t>
+          <t>1785486538</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>21.88754</t>
+          <t>193.538462</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xb963fb285adc1787ddf4ca4632c560dc9fdd9575b3cbfb29621fa14f9fd1f787</t>
+          <t>0xa6662351ed0cdd3219611c5844d3f542df082c943aa81df2efe3eb02cf0c52aa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,7 +654,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.85225</t>
+          <t>12.85893</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785460982</t>
+          <t>1785461587</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>21.87617</t>
+          <t>21.88754</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x359dd1d25732d3b83d3e7b63e7453929f93cc1f4450a4464e839d81eb8e93766</t>
+          <t>0xb963fb285adc1787ddf4ca4632c560dc9fdd9575b3cbfb29621fa14f9fd1f787</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,7 +758,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.94614</t>
+          <t>12.85225</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785460380</t>
+          <t>1785460982</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>22.035983</t>
+          <t>21.87617</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,27 +851,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x44e0e19da66aa09249da7de981a92039f9257de3fd68452ab2d431e7e40fb952</t>
+          <t>0x359dd1d25732d3b83d3e7b63e7453929f93cc1f4450a4464e839d81eb8e93766</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>12.94614</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -871,26 +875,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Cobresal vs Union La Calera</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Cobresal vs Union La Calera</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Union La Calera</t>
@@ -928,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785459482</t>
+          <t>1785460380</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>22.035983</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
+          <t>0x44e0e19da66aa09249da7de981a92039f9257de3fd68452ab2d431e7e40fb952</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785441528</t>
+          <t>1785459482</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>180.756098</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
+          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>75.41</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4038</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785441518</t>
+          <t>1785441528</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>186.773994</t>
+          <t>180.756098</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
+          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75.41</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1219,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19615611</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785345042</t>
+          <t>1785441518</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>186.773994</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
+          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1306,22 +1306,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785269304</t>
+          <t>1785345042</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>14.601681</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
+          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1443,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785196536</t>
+          <t>1785269304</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>90.961538</t>
+          <t>14.601681</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
+          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3487</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785195634</t>
+          <t>1785196536</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>102.88172</t>
+          <t>90.961538</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
+          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1635,23 +1635,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1674,7 +1682,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1712,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785193080</t>
+          <t>1785195634</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1722,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>102.88172</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1739,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
+          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1808,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785192947</t>
+          <t>1785193080</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1835,28 +1843,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
+          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1882,7 +1890,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785192847</t>
+          <t>1785192947</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,7 +1947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
+          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2016,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785192834</t>
+          <t>1785192847</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2043,7 +2051,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
+          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2120,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785192821</t>
+          <t>1785192834</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2147,23 +2155,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
+          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2224,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785192691</t>
+          <t>1785192821</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>9.367681</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,18 +2259,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
+          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19.35809</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2328,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785192659</t>
+          <t>1785192691</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2338,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>36.268084</t>
+          <t>9.367681</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,7 +2363,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
+          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2366,12 +2374,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25.4851</t>
+          <t>19.35809</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2432,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785192641</t>
+          <t>1785192659</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2442,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>48.085094</t>
+          <t>36.268084</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,28 +2467,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
+          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25.4851</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2506,7 +2514,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2536,7 +2544,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785192634</t>
+          <t>1785192641</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2546,7 +2554,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>58.874459</t>
+          <t>48.085094</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,28 +2571,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
+          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.71451</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2610,7 +2618,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2640,7 +2648,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785192633</t>
+          <t>1785192634</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2650,7 +2658,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.064505</t>
+          <t>58.874459</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,23 +2675,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
+          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.71451</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2744,7 +2752,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785192460</t>
+          <t>1785192633</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2762,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>48.064505</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,7 +2779,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
+          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2848,7 +2856,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785192458</t>
+          <t>1785192460</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2875,23 +2883,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
+          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25.41551</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2952,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785192439</t>
+          <t>1785192458</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2962,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.295506</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2979,7 +2987,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
+          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2990,12 +2998,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>25.41551</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3056,7 +3064,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785192425</t>
+          <t>1785192439</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3066,7 +3074,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>48.295506</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3083,7 +3091,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
+          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3160,7 +3168,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785192400</t>
+          <t>1785192425</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3187,7 +3195,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
+          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3198,7 +3206,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25.35348</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3264,7 +3272,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785192383</t>
+          <t>1785192400</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3274,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>48.063469</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3291,7 +3299,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
+          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3302,12 +3310,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25.3385</t>
+          <t>25.35348</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3368,7 +3376,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785192344</t>
+          <t>1785192383</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3378,7 +3386,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>47.808491</t>
+          <t>48.063469</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3395,27 +3403,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
+          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>25.3385</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3423,26 +3427,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785192020</t>
+          <t>1785192344</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>60.183673</t>
+          <t>47.808491</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3507,7 +3507,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
+          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>83.37098</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785191983</t>
+          <t>1785192020</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>167.15986</t>
+          <t>60.183673</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3619,7 +3619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
+          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21.25099</t>
+          <t>83.37098</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785191956</t>
+          <t>1785191983</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>42.608501</t>
+          <t>167.15986</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,7 +3731,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
+          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>21.25099</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785191607</t>
+          <t>1785191956</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>132.591479</t>
+          <t>42.608501</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,31 +3843,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
+          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3890,7 +3898,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3920,7 +3928,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785190879</t>
+          <t>1785191607</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3930,7 +3938,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>46.308571</t>
+          <t>132.591479</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3947,27 +3955,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
+          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.3525</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3975,26 +3979,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785190879</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>139.687943</t>
+          <t>46.308571</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,7 +4059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4074,17 +4074,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3525</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>139.687943</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,7 +4171,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4283,23 +4283,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4307,7 +4311,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4360,7 +4368,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4378,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>20.671835</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,7 +4395,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4398,17 +4406,17 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>192.07656</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4434,7 +4442,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4474,7 +4482,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>301.296565</t>
+          <t>20.671835</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4491,7 +4499,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4502,17 +4510,17 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>192.07656</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4538,7 +4546,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4568,7 +4576,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4578,7 +4586,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>323.324675</t>
+          <t>301.296565</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4595,7 +4603,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4606,17 +4614,17 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>155.6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4642,7 +4650,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4682,7 +4690,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>323.324675</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4699,27 +4707,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4.99021</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4727,11 +4731,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785189854</t>
+          <t>1785190745</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>24.643012</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99021</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785189648</t>
+          <t>1785189854</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>24.691358</t>
+          <t>24.643012</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4923,110 +4923,222 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785189648</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>24.691358</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>0x75149a4dcb7aa5d35fc6692d21303104765eb2330e7b582a2136cd6202de3543</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>2.83937</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>1.2025</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Union La Calera -1</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>Union La Calera vs Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>L19474445</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>1785189616</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>1785193200</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>14.02158</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Division/trades.xlsx
+++ b/data/sxbet/ligas/Primera Division/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xabdf4fe38efdf58bf8d47e567216699ec84fc0c25cc103f8e4cde0a12f422be5</t>
+          <t>0x1af88d6dc9fc3717babf5cf75142ac5f018099246c511d73c31b97e5e871ba5a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>56.61</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xde65f43d12cd96e371220e4b3864b8dfadf5a71d384749b19b33947eed003295</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785486538</t>
+          <t>1785507402</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>193.538462</t>
+          <t>1985.111663</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xa6662351ed0cdd3219611c5844d3f542df082c943aa81df2efe3eb02cf0c52aa</t>
+          <t>0x52c08f28916e652624c273879c2d16f5226f65a3eda58fb1acff639eea12ea5e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.85893</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785461587</t>
+          <t>1785507022</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>21.88754</t>
+          <t>17.955112</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xb963fb285adc1787ddf4ca4632c560dc9fdd9575b3cbfb29621fa14f9fd1f787</t>
+          <t>0xbb472b6ece33b6d5f9c4eae7133011f6fcf430818ecc0bb860fc9df1b1339bca</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.85225</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -779,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785460982</t>
+          <t>1785506251</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>21.87617</t>
+          <t>64.581454</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +867,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x359dd1d25732d3b83d3e7b63e7453929f93cc1f4450a4464e839d81eb8e93766</t>
+          <t>0xe3946df695661d7d619436120458ef7267956a9bdf2fb123c3b6d5d6a76e397d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12.94614</t>
+          <t>240.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.5125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785460380</t>
+          <t>1785506136</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>22.035983</t>
+          <t>469.639024</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x44e0e19da66aa09249da7de981a92039f9257de3fd68452ab2d431e7e40fb952</t>
+          <t>0x468065d91a44e3357f8a0057c79d0ea75c03b866d06b769fbb7a5359611c24b7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -970,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>408.74</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -995,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785459482</t>
+          <t>1785506026</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>827.827848</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,12 +1083,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
+          <t>0xabdf4fe38efdf58bf8d47e567216699ec84fc0c25cc103f8e4cde0a12f422be5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1082,12 +1098,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>56.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1097,24 +1113,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Cobresal vs Union La Calera</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Cobresal vs Union La Calera</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Union La Calera</t>
@@ -1122,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xde65f43d12cd96e371220e4b3864b8dfadf5a71d384749b19b33947eed003295</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785441528</t>
+          <t>1785486538</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>180.756098</t>
+          <t>193.538462</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,27 +1195,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
+          <t>0xa6662351ed0cdd3219611c5844d3f542df082c943aa81df2efe3eb02cf0c52aa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>75.41</t>
+          <t>12.85893</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4038</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1207,26 +1219,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Cobresal vs Union La Calera</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Cobresal vs Union La Calera</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Union La Calera</t>
@@ -1264,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785441518</t>
+          <t>1785461587</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>186.773994</t>
+          <t>21.88754</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,27 +1299,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
+          <t>0xb963fb285adc1787ddf4ca4632c560dc9fdd9575b3cbfb29621fa14f9fd1f787</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.85225</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1319,11 +1323,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Universidad de Concepción</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1331,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19615611</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785345042</t>
+          <t>1785460982</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>21.87617</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,39 +1403,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
+          <t>0x359dd1d25732d3b83d3e7b63e7453929f93cc1f4450a4464e839d81eb8e93766</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>12.94614</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1443,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19615611</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1480,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785269304</t>
+          <t>1785460380</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>14.601681</t>
+          <t>22.035983</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1507,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
+          <t>0x44e0e19da66aa09249da7de981a92039f9257de3fd68452ab2d431e7e40fb952</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,22 +1522,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1555,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785196536</t>
+          <t>1785459482</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>90.961538</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
+          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1642,12 +1634,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3487</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1657,7 +1649,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1667,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1712,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785195634</t>
+          <t>1785441528</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>102.88172</t>
+          <t>180.756098</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,31 +1731,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
+          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>75.41</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1771,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785193080</t>
+          <t>1785441518</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>186.773994</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,31 +1843,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
+          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Universidad de Concepción</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1875,27 +1883,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1920,17 +1928,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785192947</t>
+          <t>1785345042</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,31 +1955,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
+          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1979,27 +1995,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2024,17 +2040,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785192847</t>
+          <t>1785269304</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>14.601681</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,31 +2067,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
+          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2098,7 +2122,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2128,7 +2152,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785192834</t>
+          <t>1785196536</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2162,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>90.961538</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,31 +2179,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
+          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2202,7 +2234,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2232,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785192821</t>
+          <t>1785195634</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>102.88172</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,28 +2291,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
+          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2306,7 +2338,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2336,7 +2368,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785192691</t>
+          <t>1785193080</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2346,7 +2378,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>9.367681</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,28 +2395,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
+          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19.35809</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2410,7 +2442,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2440,7 +2472,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785192659</t>
+          <t>1785192947</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2482,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36.268084</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,7 +2499,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
+          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2478,12 +2510,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.4851</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2544,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785192641</t>
+          <t>1785192847</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2554,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.085094</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,28 +2603,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
+          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2618,7 +2650,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2648,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785192634</t>
+          <t>1785192834</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2658,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>58.874459</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2675,7 +2707,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
+          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2686,12 +2718,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25.71451</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2752,7 +2784,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785192633</t>
+          <t>1785192821</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2762,7 +2794,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.064505</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,7 +2811,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
+          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2795,7 +2827,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2856,7 +2888,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785192460</t>
+          <t>1785192691</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2866,7 +2898,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>9.367681</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,23 +2915,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
+          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19.35809</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2960,7 +2992,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785192458</t>
+          <t>1785192659</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2970,7 +3002,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>36.268084</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,7 +3019,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
+          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2998,12 +3030,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25.41551</t>
+          <t>25.4851</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3064,7 +3096,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785192439</t>
+          <t>1785192641</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3074,7 +3106,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>48.295506</t>
+          <t>48.085094</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3091,28 +3123,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
+          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3138,7 +3170,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3168,7 +3200,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785192425</t>
+          <t>1785192634</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3178,7 +3210,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>58.874459</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,7 +3227,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
+          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3206,12 +3238,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>25.71451</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3272,7 +3304,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785192400</t>
+          <t>1785192633</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3282,7 +3314,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>48.064505</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,23 +3331,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
+          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25.35348</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3376,7 +3408,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785192383</t>
+          <t>1785192460</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3386,7 +3418,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>48.063469</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3403,23 +3435,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
+          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25.3385</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3480,7 +3512,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785192344</t>
+          <t>1785192458</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3490,7 +3522,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>47.808491</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3507,27 +3539,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
+          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>25.41551</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3535,26 +3563,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3592,7 +3616,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785192020</t>
+          <t>1785192439</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3602,7 +3626,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>60.183673</t>
+          <t>48.295506</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3619,27 +3643,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
+          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>83.37098</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3647,26 +3667,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3704,7 +3720,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785191983</t>
+          <t>1785192425</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3714,7 +3730,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>167.15986</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,27 +3747,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
+          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21.25099</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3759,26 +3771,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -3816,7 +3824,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785191956</t>
+          <t>1785192400</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3826,7 +3834,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>42.608501</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,27 +3851,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
+          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>25.35348</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3871,11 +3875,7 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Union La Calera 0</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785191607</t>
+          <t>1785192383</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>132.591479</t>
+          <t>48.063469</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,28 +3955,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
+          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>25.3385</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785190879</t>
+          <t>1785192344</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>46.308571</t>
+          <t>47.808491</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,12 +4059,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
+          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4074,17 +4074,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3525</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785192020</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>139.687943</t>
+          <t>60.183673</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,12 +4171,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>83.37098</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785191983</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>167.15986</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,12 +4283,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>21.25099</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Union La Calera 0</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785191956</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>42.608501</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4395,23 +4395,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4419,7 +4423,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4472,7 +4480,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785191607</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4482,7 +4490,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>20.671835</t>
+          <t>132.591479</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4499,7 +4507,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4510,12 +4518,12 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>192.07656</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4546,7 +4554,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4576,7 +4584,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785190879</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4586,7 +4594,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>301.296565</t>
+          <t>46.308571</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4603,31 +4611,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.3525</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4650,7 +4666,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4680,7 +4696,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4690,7 +4706,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>323.324675</t>
+          <t>139.687943</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4707,31 +4723,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4754,7 +4778,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4784,7 +4808,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4794,7 +4818,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4811,7 +4835,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4826,22 +4850,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.99021</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Union La Calera -1</t>
+          <t>Union La Calera 0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4866,7 +4890,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4896,7 +4920,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785189854</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4906,7 +4930,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>24.643012</t>
+          <t>86.543641</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4923,39 +4947,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4978,7 +4994,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5008,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785189648</t>
+          <t>1785190746</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5018,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>24.691358</t>
+          <t>20.671835</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5035,110 +5051,646 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>192.07656</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.6375</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785190746</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>301.296565</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>155.6</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785190745</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>323.324675</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.8125</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785190745</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4.99021</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785189854</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>24.643012</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785189648</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>24.691358</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>0x75149a4dcb7aa5d35fc6692d21303104765eb2330e7b582a2136cd6202de3543</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>2.83937</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>1.2025</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Union La Calera -1</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>Union La Calera vs Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>L19474445</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>1785189616</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>1785193200</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>14.02158</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera Division/trades.xlsx
+++ b/data/sxbet/ligas/Primera Division/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V49"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x1af88d6dc9fc3717babf5cf75142ac5f018099246c511d73c31b97e5e871ba5a</t>
+          <t>0xf012223aca394a36db5f0f02eb7a1252e2b7ccfbdc23a99fa541f3abae29c516</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
+          <t>0x594d9bf46b0aad6cd3470cd264ba7786008325c246f03dddc3d344264918f55d</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785507402</t>
+          <t>1785539876</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1985.111663</t>
+          <t>129.74359</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x52c08f28916e652624c273879c2d16f5226f65a3eda58fb1acff639eea12ea5e</t>
+          <t>0x58e92e2d71622fed38e5f8888a5caf7c7534ab241c9a4a1ca323e1db42a5c4bc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,31 +651,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0.00269</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785507022</t>
+          <t>1785539875</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>17.955112</t>
+          <t>0.00422</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xbb472b6ece33b6d5f9c4eae7133011f6fcf430818ecc0bb860fc9df1b1339bca</t>
+          <t>0x371c701454f5e10def130d81ae9a574ff7dc21646c84dcee02bedc97cc84e614</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>24.25428</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -810,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
+          <t>0x594d9bf46b0aad6cd3470cd264ba7786008325c246f03dddc3d344264918f55d</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785506251</t>
+          <t>1785539875</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>64.581454</t>
+          <t>82.920615</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xe3946df695661d7d619436120458ef7267956a9bdf2fb123c3b6d5d6a76e397d</t>
+          <t>0x11fed80ada5920ce09be9a9b2a1a6445565901c87c45024e4f72264fd4d1e14b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>240.69</t>
+          <t>130.13523</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5125</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -914,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785506136</t>
+          <t>1785539875</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>469.639024</t>
+          <t>204.133694</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,39 +963,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x468065d91a44e3357f8a0057c79d0ea75c03b866d06b769fbb7a5359611c24b7</t>
+          <t>0xe0950c663773c5b59fd9f9ea10e00f478cbfeead52e06bc20fd3903c51f40f75</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>408.74</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.6362</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1026,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785506026</t>
+          <t>1785539857</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>827.827848</t>
+          <t>7.85853</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1067,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xabdf4fe38efdf58bf8d47e567216699ec84fc0c25cc103f8e4cde0a12f422be5</t>
+          <t>0x5c23ac37b2c940e6f51790aa8100c1fe7cdd0559a0c4bf288f28a38c9b384296</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1082,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56.61</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Universidad de Concepción 0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xde65f43d12cd96e371220e4b3864b8dfadf5a71d384749b19b33947eed003295</t>
+          <t>0x6e4b52445f363d5d2665107ddd98561199bbeb158440caa2047924f4a7aed550</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785486538</t>
+          <t>1785539852</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>193.538462</t>
+          <t>47.029126</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,31 +1179,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa6662351ed0cdd3219611c5844d3f542df082c943aa81df2efe3eb02cf0c52aa</t>
+          <t>0xd07de40ba00a35798dadd551e2d33d09729cf14ed93c545055140d1709ee9eec</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.85893</t>
+          <t>75.50999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Universidad de Concepción 0</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1227,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0x6e4b52445f363d5d2665107ddd98561199bbeb158440caa2047924f4a7aed550</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1272,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785461587</t>
+          <t>1785539849</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>21.88754</t>
+          <t>146.62134</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,23 +1291,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb963fb285adc1787ddf4ca4632c560dc9fdd9575b3cbfb29621fa14f9fd1f787</t>
+          <t>0x26f578f220440f2e10fa341cbb08611c0a1d22ab4d95487e4b29f48db0362c4e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.85225</t>
+          <t>19.55155</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1331,27 +1323,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785460982</t>
+          <t>1785539849</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>21.87617</t>
+          <t>30.911542</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,31 +1395,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x359dd1d25732d3b83d3e7b63e7453929f93cc1f4450a4464e839d81eb8e93766</t>
+          <t>0x1af88d6dc9fc3717babf5cf75142ac5f018099246c511d73c31b97e5e871ba5a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.94614</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1435,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785460380</t>
+          <t>1785507402</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>22.035983</t>
+          <t>1985.111663</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x44e0e19da66aa09249da7de981a92039f9257de3fd68452ab2d431e7e40fb952</t>
+          <t>0x52c08f28916e652624c273879c2d16f5226f65a3eda58fb1acff639eea12ea5e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1522,22 +1522,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1547,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785459482</t>
+          <t>1785507022</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>17.955112</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
+          <t>0xbb472b6ece33b6d5f9c4eae7133011f6fcf430818ecc0bb860fc9df1b1339bca</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1659,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785441528</t>
+          <t>1785506251</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>180.756098</t>
+          <t>64.581454</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,39 +1731,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
+          <t>0xe3946df695661d7d619436120458ef7267956a9bdf2fb123c3b6d5d6a76e397d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>75.41</t>
+          <t>240.69</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4038</t>
+          <t>1.5125</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -1771,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cobresal vs Union La Calera</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19624904</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785441518</t>
+          <t>1785506136</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>186.773994</t>
+          <t>469.639024</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,12 +1835,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
+          <t>0x468065d91a44e3357f8a0057c79d0ea75c03b866d06b769fbb7a5359611c24b7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1858,39 +1850,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>408.74</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Universidad de Concepción vs Audax Italiano</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Universidad de Concepción</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Universidad de Concepción</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Audax Italiano</t>
@@ -1898,7 +1890,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
+          <t>0xf50ed6a6b6bcc2d3a96578c7a959afac6db3135dba69f027f69a572007e43965</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1928,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785345042</t>
+          <t>1785506026</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1938,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>827.827848</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,12 +1947,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
+          <t>0xabdf4fe38efdf58bf8d47e567216699ec84fc0c25cc103f8e4cde0a12f422be5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1970,22 +1962,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>56.61</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1995,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Universidad de Concepción vs Audax Italiano</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Universidad de Concepción</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
+          <t>0xde65f43d12cd96e371220e4b3864b8dfadf5a71d384749b19b33947eed003295</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19615611</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2040,17 +2032,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785269304</t>
+          <t>1785486538</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>14.601681</t>
+          <t>193.538462</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,39 +2059,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
+          <t>0xa6662351ed0cdd3219611c5844d3f542df082c943aa81df2efe3eb02cf0c52aa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>12.85893</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2107,27 +2091,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2152,17 +2136,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785196536</t>
+          <t>1785461587</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>90.961538</t>
+          <t>21.88754</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,27 +2163,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
+          <t>0xb963fb285adc1787ddf4ca4632c560dc9fdd9575b3cbfb29621fa14f9fd1f787</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>12.85225</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3487</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2207,11 +2187,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2219,27 +2195,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2264,17 +2240,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785195634</t>
+          <t>1785460982</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>102.88172</t>
+          <t>21.87617</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,28 +2267,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
+          <t>0x359dd1d25732d3b83d3e7b63e7453929f93cc1f4450a4464e839d81eb8e93766</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>12.94614</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2323,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2368,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785193080</t>
+          <t>1785460380</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>22.035983</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,31 +2371,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
+          <t>0x44e0e19da66aa09249da7de981a92039f9257de3fd68452ab2d431e7e40fb952</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>23.01814</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2427,27 +2411,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,17 +2456,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785192947</t>
+          <t>1785459482</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>60.178144</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,31 +2483,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
+          <t>0xe254c753e527d9426ac3325c4e85f4d42e6404fa1462296c8e2491df27378b41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2531,27 +2523,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2576,17 +2568,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785192847</t>
+          <t>1785441528</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>180.756098</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,31 +2595,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
+          <t>0x198b502814d8debd85b628ffc8f53eaaae98987f90ece7198c8e00dcdde84681</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>75.41</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2635,27 +2635,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Cobresal vs Union La Calera</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Everton Vina Del Mar</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd4128e9b4a0256088f67de6bb81a94360d3a5478da17faa1825ab7853a92ba6a</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19624904</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2680,17 +2680,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785192834</t>
+          <t>1785441518</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>186.773994</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,31 +2707,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
+          <t>0x604f7109712a70b0694c8ec8cab14f6f0f677fd0ce9e1138af3df6e3f3198407</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25.83486</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Universidad de Concepción</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2739,27 +2747,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x47fdcecfa4d2732b518462d69c7594643308e6a756789812a6ed0bde26235c1d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2784,17 +2792,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785192821</t>
+          <t>1785345042</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.064856</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,31 +2819,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
+          <t>0x0693afbc49b8dfaac7c178344cd8f3ad06c35dbe766446ac310597197412110a</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2843,27 +2859,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
+          <t>Universidad de Concepción vs Audax Italiano</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Universidad de Concepción</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Everton Vina Del Mar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x9639ae2c7d4ff15b225e1ea23ea6bfc724318f55c1b34829404f600c3bbe38ea</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19474445</t>
+          <t>L19615611</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2888,17 +2904,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785192691</t>
+          <t>1785269304</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785193200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>9.367681</t>
+          <t>14.601681</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,31 +2931,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
+          <t>0xf2abad6809206f17d3394fc712d0bcda06c640c35552616aa47def3ca29e0354</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19.35809</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -2962,7 +2986,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2992,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785192659</t>
+          <t>1785196536</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3002,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>36.268084</t>
+          <t>90.961538</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3019,31 +3043,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
+          <t>0x7bbbb98799471ffff03e1a334b9834c14eae14b7466cc135b12f7f2b51e9d345</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25.4851</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -3066,7 +3098,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd1c0086fb8f65565a83bdeb612857be4a9f6fe0dfac3be79c4158b27f240bd8b</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3096,7 +3128,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785192641</t>
+          <t>1785195634</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3106,7 +3138,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>48.085094</t>
+          <t>102.88172</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3123,7 +3155,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
+          <t>0x1319ae8b64d5108fb753e7fc61b0f159a3472fe4cf071e5676e258291b17ec59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3134,17 +3166,17 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3170,7 +3202,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3200,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785192634</t>
+          <t>1785193080</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3210,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>58.874459</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3227,28 +3259,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
+          <t>0x2331cad34749bcb25720fab56c46332d1537ce38fd4e3a396962ae7120037812</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25.71451</t>
+          <t>23.01814</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3274,7 +3306,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0xd3d626491f31c471d5d4e30f1daa5a3c25eb87f58855e48167d8ee28b7e36cc6</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3304,7 +3336,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785192633</t>
+          <t>1785192947</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3314,7 +3346,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>48.064505</t>
+          <t>60.178144</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,23 +3363,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
+          <t>0xab93fd44f60c9d84a78b664b016783e0232a9bb482369fe6a2d46ed9a45441e6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3408,7 +3440,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785192460</t>
+          <t>1785192847</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3418,7 +3450,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3435,23 +3467,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
+          <t>0xb8580e609937bc441f1e334f3f6533b0c6c756a8381d14f977211f946a37fa82</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3512,7 +3544,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785192458</t>
+          <t>1785192834</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3522,7 +3554,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>9.456265</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3539,7 +3571,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
+          <t>0xa8f45674caae9f0d42042fffaf4a3d13c143c1907ecd88a576b51cd1167a5c59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3550,12 +3582,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>25.41551</t>
+          <t>25.83486</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3616,7 +3648,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785192439</t>
+          <t>1785192821</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3626,7 +3658,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48.295506</t>
+          <t>48.064856</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,23 +3675,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
+          <t>0x768f6191dbc6372205f43c4467eed5fc015b275de340019052829b5f17d1e3df</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3720,7 +3752,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785192425</t>
+          <t>1785192691</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3730,7 +3762,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>9.367681</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3747,7 +3779,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
+          <t>0x89c3d3d76618fbccf752fbec3580c925158f893ebfdb9ad1563375ba778321d8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3758,12 +3790,12 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>25.36465</t>
+          <t>19.35809</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3824,7 +3856,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785192400</t>
+          <t>1785192659</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3834,7 +3866,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>48.084645</t>
+          <t>36.268084</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3851,7 +3883,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
+          <t>0x7e3329d355bb1f900d79e4dbf7a858855991f721f2bdf3fb475cb05d6bc7a188</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3862,12 +3894,12 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25.35348</t>
+          <t>25.4851</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3928,7 +3960,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785192383</t>
+          <t>1785192641</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +3970,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>48.063469</t>
+          <t>48.085094</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,28 +3987,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
+          <t>0x07829ae4146f1c530796799fb22712b8e8abbd807c42fbbe2cccd6e92b34edf9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25.3385</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4002,7 +4034,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+          <t>0x18fcbe753af86aea84ff4fc1336c091ef27fed211fad3f3d0ba7658412f5873d</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4032,7 +4064,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785192344</t>
+          <t>1785192634</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4074,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>47.808491</t>
+          <t>58.874459</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,27 +4091,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
+          <t>0x1e34b64cf041212de73b053ecfe9ab1c057ed47b48b287cee37ab768cdcb474a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>25.71451</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4087,26 +4115,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -4144,7 +4168,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785192020</t>
+          <t>1785192633</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4154,7 +4178,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>60.183673</t>
+          <t>48.064505</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,27 +4195,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
+          <t>0x2ce7d4510759d319390e2d4c2104cbbfd3b370cdaeeef2726778cdb0ce74a08b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>83.37098</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4199,26 +4219,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -4256,7 +4272,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785191983</t>
+          <t>1785192460</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4282,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>167.15986</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,27 +4299,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
+          <t>0x21aaa4195f9736b36e968c1e6b9a8303b47d06e67307db840644e0a5bc93200a</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21.25099</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4311,26 +4323,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -4368,7 +4376,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785191956</t>
+          <t>1785192458</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4378,7 +4386,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>42.608501</t>
+          <t>9.456265</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4395,27 +4403,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
+          <t>0xfcc5c548186e99f84799d34b20b3536c5ba0181036040d2a42464fbbdb7417e0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>25.41551</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4423,11 +4427,7 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Union La Calera 0</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785191607</t>
+          <t>1785192439</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>132.591479</t>
+          <t>48.295506</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4507,28 +4507,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
+          <t>0x8e401b0e5d16328663aac18e423af87098ea1dda6e24d1dde66a592924f43d1d</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Primera Division</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785190879</t>
+          <t>1785192425</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>46.308571</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4611,7 +4611,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
+          <t>0x2602f058fc105f294f076dd1e5005349e418f6ec64c52918b0f5bebd650ca211</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4619,46 +4619,38 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>25.36465</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3525</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -4666,7 +4658,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4696,7 +4688,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785192400</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4706,7 +4698,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>139.687943</t>
+          <t>48.084645</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,7 +4715,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+          <t>0xb0348ed23970220d589cf73d0d8e1e599c35edffcdde0fc88cce09a3094c18fa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4731,19 +4723,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>25.35348</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4751,26 +4739,22 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Union La Calera vs Everton Vina Del Mar</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
@@ -4808,7 +4792,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785192383</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4818,7 +4802,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>48.063469</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,7 +4819,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+          <t>0xd128d817302e305b7bba7256d2e17c89b015cbd14629f51f1d633e3b77848312</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4843,19 +4827,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>25.3385</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4863,11 +4843,7 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Union La Calera 0</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4890,7 +4866,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4920,7 +4896,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785190811</t>
+          <t>1785192344</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4906,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>86.543641</t>
+          <t>47.808491</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,23 +4923,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+          <t>0x0fc50b5b48b21d68168123f8c2107e7c056f31336cc55d6fe63a5d6ac33743d4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4971,7 +4951,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -4994,7 +4978,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5024,7 +5008,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785192020</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5018,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>20.671835</t>
+          <t>60.183673</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,31 +5035,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+          <t>0xcf92979cf4b6c1f18afb8b80d8fedb96dc4aef634a20bc229dd9b2653cbe7d5d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>192.07656</t>
+          <t>83.37098</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -5098,7 +5090,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5128,7 +5120,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785190746</t>
+          <t>1785191983</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5138,7 +5130,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>301.296565</t>
+          <t>167.15986</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,23 +5147,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+          <t>0xa1d79d117fe8c3c569f91fc4ccd1428d6a2096461bc0dcdeb17fef7eae531b3b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>21.25099</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5179,7 +5175,11 @@
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785191956</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>323.324675</t>
+          <t>42.608501</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5259,31 +5259,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+          <t>0x441cdc90c321f5eb6838df61fa5f462509f68d5945b4591381cfc6eeeefd8263</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -5306,7 +5314,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5336,7 +5344,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785190745</t>
+          <t>1785191607</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5346,7 +5354,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>132.591479</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5363,39 +5371,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+          <t>0x2edc1979c9a1ebec3be9b497272f55f15e12fb39dc5c28df5c93c4de916461f0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.99021</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Union La Calera -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Primera Division</t>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0x0bf1543550e586b840ea5a18d0859b353683940dc0f4727909e37d6cfb50a597</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785189854</t>
+          <t>1785190879</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>24.643012</t>
+          <t>46.308571</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5475,12 +5475,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+          <t>0xfeac3d5b8b37fb246f7923c705f9eca7f408690dae8cd79ad71bd990bb473322</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5490,22 +5490,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.2025</t>
+          <t>1.3525</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Union La Calera -1</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785189648</t>
+          <t>1785190811</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>24.691358</t>
+          <t>139.687943</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5587,110 +5587,974 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>0x6769da4edcc9e1ecb099281bf7217dbe2dbd12aae6a47e68db75133b5359bb88</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>43.38</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.5012</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785190811</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>86.543641</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x22d1fafa8088da7f7a2b8f0bf4958eac45d0e3a6717af64097c4193bd3f20791</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>43.38</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.5012</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Union La Calera 0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785190811</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>86.543641</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x2c87bdc1ce90745088ffd9ebd96af71b905f18c024ee4ca9b9527c9ef80e8649</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.4838</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x1acd074a731088ace7e21cd244890db1057b4e161c6a98610d5c702cca64a543</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785190746</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>20.671835</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x0d35fbd0614e56309f6312343d9fd31534a4a594657dc5140f8222085701fa49</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>192.07656</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.6375</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0xc2859a95eee4f6775ee94d9ceec98bf09c72f340a5caa3ab3b3414d1f568dc5f</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785190746</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>301.296565</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0xd4597e91c7afcc176a2724de8c484c9b64308f563c8cac755f2134bcbbf21624</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>155.6</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x514837a9473437ab2cf466521fe68cba7c19c234823524ad3fbdbdce7cf4794c</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785190745</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>323.324675</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x691203d05ab4530ec4150cea8bc2df09ea161503390d0fcc90365067e963b2fc</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.8125</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785190745</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0xa498608fd9bb562f19a04057444a68be42b16583a563ac90c6952b78a8d64bf2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4.99021</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785189854</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>24.643012</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x4917d8c9cd8bff5395e7a03b6861ece115b6a6e1c3ed38c85a71e5950335baa5</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.2025</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Union La Calera -1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Union La Calera vs Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Everton Vina Del Mar</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19474445</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785189648</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785193200</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>24.691358</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>0x75149a4dcb7aa5d35fc6692d21303104765eb2330e7b582a2136cd6202de3543</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>2.83937</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>1.2025</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Union La Calera -1</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Primera Division</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>Union La Calera vs Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Union La Calera</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Everton Vina Del Mar</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>0x642f4b45a3e6a3bf4f14d5aa6f4f17b6be01fea1c325fa8b80c04c20cd60e201</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>L19474445</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>1785189616</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>1785193200</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>14.02158</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
